--- a/panchang-data/JagannathPuri2026.xlsx
+++ b/panchang-data/JagannathPuri2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dwivedi\Desktop\Base Files To Make New Panchang Excel Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jyotishiji.com\Base Files To Make New Panchang Excel Files\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0482FC4-81E6-4BF5-B229-DAB47B076FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80A9DCED-5CB0-4F21-8491-03942762EC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{8C3F8180-4D61-4E4F-8E46-68C75EBE2B4E}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{E49716D2-DE16-431A-98A8-DA95DDEC35DA}"/>
   </bookViews>
   <sheets>
-    <sheet name="WORD_952" sheetId="1" r:id="rId1"/>
+    <sheet name="WORD_954" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WORD_952!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">WORD_954!$A$1:$AB$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -16613,7 +16613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B4614DD-FB58-4CEA-893B-4C2FDC73AB66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DFD06B-1DC4-4E6E-BAEC-84197172A237}">
   <dimension ref="A1:AB366"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
@@ -48103,7 +48103,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB1" xr:uid="{3B4614DD-FB58-4CEA-893B-4C2FDC73AB66}"/>
+  <autoFilter ref="A1:AB1" xr:uid="{F5DFD06B-1DC4-4E6E-BAEC-84197172A237}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/panchang-data/JagannathPuri2026.xlsx
+++ b/panchang-data/JagannathPuri2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5401">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16228,6 +16228,9 @@
   </si>
   <si>
     <t>121°05'10.16</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16717,7 +16720,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16803,7 +16806,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16889,7 +16892,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16975,7 +16978,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17061,7 +17064,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17147,7 +17150,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17233,7 +17236,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17319,7 +17322,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17405,7 +17408,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17491,7 +17494,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17577,7 +17580,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17663,7 +17666,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17749,7 +17752,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17835,7 +17838,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17921,7 +17924,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18007,7 +18010,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18093,7 +18096,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18179,7 +18182,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18265,7 +18268,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18351,7 +18354,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18437,7 +18440,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18523,7 +18526,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18609,7 +18612,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18695,7 +18698,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18781,7 +18784,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18867,7 +18870,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18953,7 +18956,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19039,7 +19042,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19125,7 +19128,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19211,7 +19214,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19297,7 +19300,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19383,7 +19386,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19469,7 +19472,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19555,7 +19558,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19641,7 +19644,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19727,7 +19730,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19813,7 +19816,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19899,7 +19902,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19985,7 +19988,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20071,7 +20074,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20157,7 +20160,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20243,7 +20246,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20329,7 +20332,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20415,7 +20418,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20501,7 +20504,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20587,7 +20590,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20673,7 +20676,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20759,7 +20762,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20845,7 +20848,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20931,7 +20934,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21017,7 +21020,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21103,7 +21106,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21189,7 +21192,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21275,7 +21278,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21361,7 +21364,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21447,7 +21450,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21533,7 +21536,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21619,7 +21622,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21705,7 +21708,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21791,7 +21794,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21877,7 +21880,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21963,7 +21966,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22049,7 +22052,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22135,7 +22138,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22221,7 +22224,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22307,7 +22310,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22393,7 +22396,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22479,7 +22482,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22565,7 +22568,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22651,7 +22654,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22737,7 +22740,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22823,7 +22826,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22909,7 +22912,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22995,7 +22998,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23081,7 +23084,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23167,7 +23170,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23253,7 +23256,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23339,7 +23342,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23425,7 +23428,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23511,7 +23514,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23597,7 +23600,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23683,7 +23686,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23769,7 +23772,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23855,7 +23858,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23941,7 +23944,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24027,7 +24030,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24113,7 +24116,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24199,7 +24202,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24285,7 +24288,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24371,7 +24374,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24457,7 +24460,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24543,7 +24546,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24629,7 +24632,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24715,7 +24718,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24801,7 +24804,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24887,7 +24890,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24973,7 +24976,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25059,7 +25062,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25145,7 +25148,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25231,7 +25234,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25317,7 +25320,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25403,7 +25406,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25489,7 +25492,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25575,7 +25578,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25661,7 +25664,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25747,7 +25750,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25833,7 +25836,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25919,7 +25922,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26005,7 +26008,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26091,7 +26094,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26177,7 +26180,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26263,7 +26266,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26349,7 +26352,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26435,7 +26438,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26521,7 +26524,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26607,7 +26610,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26693,7 +26696,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26779,7 +26782,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26865,7 +26868,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26951,7 +26954,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27037,7 +27040,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27123,7 +27126,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27209,7 +27212,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27295,7 +27298,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27381,7 +27384,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27467,7 +27470,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27553,7 +27556,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27639,7 +27642,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27725,7 +27728,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27811,7 +27814,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27897,7 +27900,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27983,7 +27986,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28069,7 +28072,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28155,7 +28158,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28241,7 +28244,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28327,7 +28330,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1874</v>
+        <v>2311</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28413,7 +28416,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28499,7 +28502,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28585,7 +28588,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28671,7 +28674,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28757,7 +28760,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28843,7 +28846,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28929,7 +28932,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29015,7 +29018,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29101,7 +29104,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29187,7 +29190,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29273,7 +29276,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29359,7 +29362,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29445,7 +29448,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29531,7 +29534,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29617,7 +29620,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1874</v>
+        <v>5400</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29703,7 +29706,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29789,7 +29792,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29875,7 +29878,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29961,7 +29964,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30047,7 +30050,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30133,7 +30136,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30219,7 +30222,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30305,7 +30308,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30391,7 +30394,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30477,7 +30480,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30563,7 +30566,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30649,7 +30652,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30735,7 +30738,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30821,7 +30824,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30907,7 +30910,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2311</v>
+        <v>5400</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
